--- a/data/raw/inventory/Week 34/White_Mulberry/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 34/White_Mulberry/Seller FBA Inventory (SP-API).xlsx
@@ -709,7 +709,7 @@
         <v>11</v>
       </c>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -721,7 +721,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>11</v>
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F6" t="n">
         <v>47</v>
@@ -783,13 +783,13 @@
         <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>49</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="F7" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -845,10 +845,10 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1140,10 +1140,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1158,7 +1158,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L12" t="n">
         <v>3</v>
@@ -1326,25 +1326,25 @@
         </is>
       </c>
       <c r="E15" t="n">
+        <v>104</v>
+      </c>
+      <c r="F15" t="n">
+        <v>102</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
         <v>105</v>
-      </c>
-      <c r="F15" t="n">
-        <v>105</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>106</v>
       </c>
       <c r="L15" t="n">
         <v>1</v>
@@ -1574,10 +1574,10 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="F19" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1592,10 +1592,10 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="L19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -1716,10 +1716,10 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>89</v>
+        <v>38</v>
       </c>
       <c r="F22" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1775,13 +1775,13 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="K22" t="n">
-        <v>91</v>
+        <v>39</v>
       </c>
       <c r="L22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2073,7 +2073,7 @@
         <v>68</v>
       </c>
       <c r="F27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -2085,7 +2085,7 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K27" t="n">
         <v>89</v>
@@ -2507,19 +2507,19 @@
         <v>186</v>
       </c>
       <c r="F34" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K34" t="n">
         <v>191</v>

--- a/data/raw/inventory/Week 34/White_Mulberry/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 34/White_Mulberry/Seller FBA Inventory (SP-API).xlsx
@@ -771,7 +771,7 @@
         <v>49</v>
       </c>
       <c r="F6" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -783,7 +783,7 @@
         <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>49</v>
@@ -1574,10 +1574,10 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F19" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="L19" t="n">
         <v>2</v>
